--- a/onboarding_forms/030_store_employee_orientation_registration_form--onboarding_forms.xlsx
+++ b/onboarding_forms/030_store_employee_orientation_registration_form--onboarding_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time', 'value': 'full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time', 'value': 'part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'location_1',_'value':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Location 1', 'value': 'location_1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'location_2',_'value':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Location 2', 'value': 'location_2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'schedule_1',_'value':_'schedule_1'}</t>
+          <t>schedule_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Schedule 1', 'value': 'schedule_1'}</t>
+          <t>Schedule 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'schedule_2',_'value':_'schedule_2'}</t>
+          <t>schedule_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Schedule 2', 'value': 'schedule_2'}</t>
+          <t>Schedule 2</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Monday', 'value': 'monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday', 'value': 'tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday', 'value': 'wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday', 'value': 'thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Friday', 'value': 'friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday', 'value': 'saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday', 'value': 'sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'morning',_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Morning', 'value': 'morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon',_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon', 'value': 'afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'night',_'value':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Night', 'value': 'night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'spouse',_'value':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse', 'value': 'spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'partner',_'value':_'partner'}</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Partner', 'value': 'partner'}</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'self',_'value':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Self', 'value': 'self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
